--- a/output/full_scan/batch_seq6_2026-07-14.xlsx
+++ b/output/full_scan/batch_seq6_2026-07-14.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -580,21 +580,21 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6241</v>
+        <v>6226</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>807.1807657482764</v>
+        <v>954.4554672435424</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17.7</v>
+        <v>25.85</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>76.80394518446079</v>
+        <v>72.62693201948136</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>43.90651807209025</v>
+        <v>39.74495239982538</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.818076574827633</v>
+        <v>0.3935020161603398</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1229672118522091</v>
+        <v>0.5317991666378723</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6270</v>
+        <v>6241</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>706.5206639731175</v>
+        <v>807.1807657482764</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33.9</v>
+        <v>17.7</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45.83444848126763</v>
+        <v>76.80394518446079</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>43.75043536784347</v>
+        <v>43.90651807209025</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3620886250542646</v>
+        <v>3.818076574827633</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.824255774970226</v>
+        <v>0.1229672118522091</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6175</v>
+        <v>6270</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>703.516963338785</v>
+        <v>706.5206639731175</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>102.5</v>
+        <v>33.9</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>48.52913609226912</v>
+        <v>45.83444848126763</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>31.82593940721029</v>
+        <v>43.75043536784347</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.4543882569655545</v>
+        <v>0.3620886250542646</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-2.224662246525937</v>
+        <v>-0.824255774970226</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6416</v>
+        <v>6175</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>682.3566867669115</v>
+        <v>703.516963338785</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>102.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>72.48187230479999</v>
+        <v>48.52913609226912</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>29.01416920561945</v>
+        <v>31.82593940721029</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.835668676691143</v>
+        <v>0.4543882569655545</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.127622203069515</v>
+        <v>-2.224662246525937</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6409</v>
+        <v>6416</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>654.8992229803284</v>
+        <v>682.3566867669115</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1080</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>55.84507125515795</v>
+        <v>72.48187230479999</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44.93231926036314</v>
+        <v>29.01416920561945</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.8265556699763907</v>
+        <v>1.835668676691143</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-9.397335881346891</v>
+        <v>2.127622203069515</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6446</v>
+        <v>6409</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>626.3896488782319</v>
+        <v>654.8992229803284</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>51.05135197217093</v>
+        <v>55.84507125515795</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>48.41063957168656</v>
+        <v>44.93231926036314</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.26409236192915</v>
+        <v>0.8265556699763907</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-19.10510148502476</v>
+        <v>-9.397335881346891</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6173</v>
+        <v>6446</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>625.7057062661002</v>
+        <v>626.3896488782319</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>239</v>
+        <v>1200</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>43.27983496844004</v>
+        <v>51.05135197217093</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>26.27010618009322</v>
+        <v>48.41063957168656</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.991145553584312</v>
+        <v>1.26409236192915</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-12.86191914999044</v>
+        <v>-19.10510148502476</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6223</v>
+        <v>6173</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>625.4361976776689</v>
+        <v>625.7057062661002</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6340</v>
+        <v>239</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>48.81368454197317</v>
+        <v>43.27983496844004</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>23.8279116587089</v>
+        <v>26.27010618009322</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.9136641720624714</v>
+        <v>1.991145553584312</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-60.96832976587609</v>
+        <v>-12.86191914999044</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6202</v>
+        <v>6223</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>617.3481223318529</v>
+        <v>625.4361976776689</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>67.7</v>
+        <v>6340</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>53.25845539116474</v>
+        <v>48.81368454197317</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>27.90733535117911</v>
+        <v>23.8279116587089</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7270229980989944</v>
+        <v>0.9136641720624714</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.0857897946341457</v>
+        <v>-60.96832976587609</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6477</v>
+        <v>6202</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>609.3300350955575</v>
+        <v>617.3481223318529</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>41.5</v>
+        <v>67.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>67.324048459271</v>
+        <v>53.25845539116474</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>26.91753443877696</v>
+        <v>27.90733535117911</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4.033003509555744</v>
+        <v>0.7270229980989944</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.9792696858328648</v>
+        <v>-0.0857897946341457</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6243</v>
+        <v>6477</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>605.4219371961967</v>
+        <v>609.3300350955575</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>39.65</v>
+        <v>41.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>54.40197818647197</v>
+        <v>67.324048459271</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>26.77070390363494</v>
+        <v>26.91753443877696</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.223424028850215</v>
+        <v>4.033003509555744</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.391333699908873</v>
+        <v>0.9792696858328648</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6182</v>
+        <v>6243</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>595.7065043249268</v>
+        <v>605.4219371961967</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>186.5</v>
+        <v>39.65</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>75.28154415979259</v>
+        <v>54.40197818647197</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>43.78305742437477</v>
+        <v>26.77070390363494</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.710171550431297</v>
+        <v>1.223424028850215</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>4.440058799228382</v>
+        <v>-0.391333699908873</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6432</v>
+        <v>6182</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>592.6694626055988</v>
+        <v>595.7065043249268</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>74.2</v>
+        <v>186.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>51.9318770265015</v>
+        <v>75.28154415979259</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>26.99536474116338</v>
+        <v>43.78305742437477</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.465586324897158</v>
+        <v>1.710171550431297</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1.221190051373759</v>
+        <v>4.440058799228382</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6257</v>
+        <v>6432</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>592.3181448627982</v>
+        <v>592.6694626055988</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>225</v>
+        <v>74.2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46.32457444120142</v>
+        <v>51.9318770265015</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20.92933929602484</v>
+        <v>26.99536474116338</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7125251154089224</v>
+        <v>0.465586324897158</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-2.229376317344951</v>
+        <v>-1.221190051373759</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6464</v>
+        <v>6257</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>570.8329835930887</v>
+        <v>592.3181448627982</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.22656049900553</v>
+        <v>46.32457444120142</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>24.8947885791952</v>
+        <v>20.92933929602484</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.334993426864302</v>
+        <v>0.7125251154089224</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0190707261024043</v>
+        <v>-2.229376317344951</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6197</v>
+        <v>6464</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>566.2334157767323</v>
+        <v>570.8329835930887</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>322</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>44.89359437845828</v>
+        <v>54.22656049900553</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.05534510108968</v>
+        <v>24.8947885791952</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8715988546012939</v>
+        <v>2.334993426864302</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-7.292074804727005</v>
+        <v>0.0190707261024043</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6168</v>
+        <v>6197</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>561.2678130962072</v>
+        <v>566.2334157767323</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>26.85</v>
+        <v>322</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>42.76775226738852</v>
+        <v>44.89359437845828</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21.76487957497193</v>
+        <v>36.05534510108968</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3633425419124129</v>
+        <v>0.8715988546012939</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.4747294013211813</v>
+        <v>-7.292074804727005</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6191</v>
+        <v>6168</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>559.3986028059901</v>
+        <v>561.2678130962072</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>96.2</v>
+        <v>26.85</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>42.65586210564621</v>
+        <v>42.76775226738852</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.82279381065266</v>
+        <v>21.76487957497193</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5929751870397733</v>
+        <v>0.3633425419124129</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.7961131377913229</v>
+        <v>-0.4747294013211813</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6204</v>
+        <v>6191</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>557.5847612184569</v>
+        <v>559.3986028059901</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>89</v>
+        <v>96.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>35.76575857171299</v>
+        <v>42.65586210564621</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>28.45149686268865</v>
+        <v>25.82279381065266</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4631501881566225</v>
+        <v>0.5929751870397733</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-4.555498696300624</v>
+        <v>-0.7961131377913229</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6472</v>
+        <v>6204</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>541.5011723614942</v>
+        <v>557.5847612184569</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>413</v>
+        <v>89</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>49.2285197213361</v>
+        <v>35.76575857171299</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>30.65263089338858</v>
+        <v>28.45149686268865</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5855501490300912</v>
+        <v>0.4631501881566225</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-2.350891523624778</v>
+        <v>-4.555498696300624</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6259</v>
+        <v>6472</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>532.0646771200247</v>
+        <v>541.5011723614942</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>37.5</v>
+        <v>413</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>54.77021955744483</v>
+        <v>49.2285197213361</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>34.72209896603601</v>
+        <v>30.65263089338858</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7113393342128175</v>
+        <v>0.5855501490300912</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.4985840994407651</v>
+        <v>-2.350891523624778</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6165</v>
+        <v>6259</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>528.6300978340835</v>
+        <v>532.0646771200247</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>50.4</v>
+        <v>37.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>56.5386938634558</v>
+        <v>54.77021955744483</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21.31155343297752</v>
+        <v>34.72209896603601</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.118349798625071</v>
+        <v>0.7113393342128175</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.3010316743600115</v>
+        <v>-0.4985840994407651</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6196</v>
+        <v>6165</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>524.6186672803832</v>
+        <v>528.6300978340835</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>539</v>
+        <v>50.4</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>50.89281057762744</v>
+        <v>56.5386938634558</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>25.26123613905684</v>
+        <v>21.31155343297752</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8129072181677597</v>
+        <v>1.118349798625071</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-6.530133867101249</v>
+        <v>0.3010316743600115</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6277</v>
+        <v>6196</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>518.6623768134448</v>
+        <v>524.6186672803832</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>74.09999999999999</v>
+        <v>539</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>58.38830669987056</v>
+        <v>50.89281057762744</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26.51673560444614</v>
+        <v>25.26123613905684</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.494037212787213</v>
+        <v>0.8129072181677597</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.4568128013495007</v>
+        <v>-6.530133867101249</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6271</v>
+        <v>6277</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>517.9183904601116</v>
+        <v>518.6623768134448</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>225.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>44.22804903206558</v>
+        <v>58.38830669987056</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21.93671298652433</v>
+        <v>26.51673560444614</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5371767043153114</v>
+        <v>2.494037212787213</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-5.331569143827013</v>
+        <v>0.4568128013495007</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6207</v>
+        <v>6271</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>505.0012182628007</v>
+        <v>517.9183904601116</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>135</v>
+        <v>225.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>48.84109807812109</v>
+        <v>44.22804903206558</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>41.85380183489033</v>
+        <v>21.93671298652433</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7131684038979115</v>
+        <v>0.5371767043153114</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-3.994354329441958</v>
+        <v>-5.331569143827013</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6214</v>
+        <v>6207</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>502.9904858780998</v>
+        <v>505.0012182628007</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>140.5</v>
+        <v>135</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>56.21141223163128</v>
+        <v>48.84109807812109</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>16.14698795744424</v>
+        <v>41.85380183489033</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8518047790985974</v>
+        <v>0.7131684038979115</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.6842795324855271</v>
+        <v>-3.994354329441958</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6423</v>
+        <v>6214</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>502.0694205664687</v>
+        <v>502.9904858780998</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>140.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>34.16315805100324</v>
+        <v>56.21141223163128</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24.27430426004514</v>
+        <v>16.14698795744424</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.822545002015295</v>
+        <v>0.8518047790985974</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.25504946675641</v>
+        <v>0.6842795324855271</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6213</v>
+        <v>6423</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>498.5450687156355</v>
+        <v>502.0694205664687</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>348.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.85438543692747</v>
+        <v>34.16315805100324</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>25.08427676646858</v>
+        <v>24.27430426004514</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.817979765761531</v>
+        <v>1.822545002015295</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.8007752735410705</v>
+        <v>0.25504946675641</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6291</v>
+        <v>6213</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>488.4295322642837</v>
+        <v>498.5450687156355</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>428</v>
+        <v>348.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>36.28524597822436</v>
+        <v>54.85438543692747</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>17.38130521268268</v>
+        <v>25.08427676646858</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6569618328341066</v>
+        <v>0.817979765761531</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-16.12609477048321</v>
+        <v>-0.8007752735410705</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6208</v>
+        <v>6291</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>485.9152310552133</v>
+        <v>488.4295322642837</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>428</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>41.85209954337073</v>
+        <v>36.28524597822436</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>16.77569412115935</v>
+        <v>17.38130521268268</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2921451922553532</v>
+        <v>0.6569618328341066</v>
       </c>
       <c r="K33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-1.698945082025703</v>
+        <v>-16.12609477048321</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6220</v>
+        <v>6208</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>484.1290094227344</v>
+        <v>485.9152310552133</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>35.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>53.86870912882564</v>
+        <v>41.85209954337073</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>36.36956667652078</v>
+        <v>16.77569412115935</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.572551470345447</v>
+        <v>0.2921451922553532</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.2508775512152084</v>
+        <v>-1.698945082025703</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6261</v>
+        <v>6220</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>470.5799195337718</v>
+        <v>484.1290094227344</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>88.7</v>
+        <v>35.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>37.06298179138761</v>
+        <v>53.86870912882564</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>18.38318011155575</v>
+        <v>36.36956667652078</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.736120303907918</v>
+        <v>1.572551470345447</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0841506895193324</v>
+        <v>-0.2508775512152084</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6279</v>
+        <v>6261</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>467.0978458533666</v>
+        <v>470.5799195337718</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>121</v>
+        <v>88.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.4881799992375</v>
+        <v>37.06298179138761</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>19.36431565585194</v>
+        <v>18.38318011155575</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7338725922490119</v>
+        <v>1.736120303907918</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1192453578751319</v>
+        <v>-0.0841506895193324</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6414</v>
+        <v>6279</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>462.4311605315012</v>
+        <v>467.0978458533666</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>377.5</v>
+        <v>121</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>50.47727631051494</v>
+        <v>52.4881799992375</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>18.95384540707514</v>
+        <v>19.36431565585194</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.122261892935205</v>
+        <v>0.7338725922490119</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0559150484867396</v>
+        <v>0.1192453578751319</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6239</v>
+        <v>6414</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>459.0641023336239</v>
+        <v>462.4311605315012</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>304</v>
+        <v>377.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43.36660157767685</v>
+        <v>50.47727631051494</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>21.50974862709917</v>
+        <v>18.95384540707514</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7336466698239531</v>
+        <v>1.122261892935205</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-5.618728576515172</v>
+        <v>0.0559150484867396</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6435</v>
+        <v>6239</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>453.9066332604601</v>
+        <v>459.0641023336239</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>334</v>
+        <v>304</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.72409813063921</v>
+        <v>43.36660157767685</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>31.33510564529017</v>
+        <v>21.50974862709917</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7906633260460061</v>
+        <v>0.7336466698239531</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-5.805329107244486</v>
+        <v>-5.618728576515172</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6190</v>
+        <v>6435</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>448.0993243156416</v>
+        <v>453.9066332604601</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>75.7</v>
+        <v>334</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>39.61076499582426</v>
+        <v>49.72409813063921</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16.43232032582277</v>
+        <v>31.33510564529017</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6927300542397613</v>
+        <v>0.7906633260460061</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.9165354898786572</v>
+        <v>-5.805329107244486</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6411</v>
+        <v>6190</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>443.8782058166808</v>
+        <v>448.0993243156416</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>40.54821657971687</v>
+        <v>39.61076499582426</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>21.81505885552768</v>
+        <v>16.43232032582277</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6572174049761657</v>
+        <v>0.6927300542397613</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.534996092610094</v>
+        <v>-0.9165354898786572</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6282</v>
+        <v>6411</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>441.7583193195437</v>
+        <v>443.8782058166808</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>54.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>44.22733739969837</v>
+        <v>40.54821657971687</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.43952883284172</v>
+        <v>21.81505885552768</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.8961723518244209</v>
+        <v>0.6572174049761657</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.3815774989260569</v>
+        <v>-1.534996092610094</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6215</v>
+        <v>6282</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>440.2805390976282</v>
+        <v>441.7583193195437</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>105</v>
+        <v>54.8</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>42.97615261544859</v>
+        <v>44.22733739969837</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>17.01092730832067</v>
+        <v>21.43952883284172</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7692535877974577</v>
+        <v>0.8961723518244209</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.4717411129644382</v>
+        <v>-0.3815774989260569</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6166</v>
+        <v>6215</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>432.5648148351137</v>
+        <v>440.2805390976282</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>132.5</v>
+        <v>105</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.04532741358583</v>
+        <v>42.97615261544859</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>32.85635345946328</v>
+        <v>17.01092730832067</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4852319860714957</v>
+        <v>0.7692535877974577</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-2.166266605633122</v>
+        <v>0.4717411129644382</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6292</v>
+        <v>6166</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>424.5421983757583</v>
+        <v>432.5648148351137</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>53.6</v>
+        <v>132.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>38.53082018490008</v>
+        <v>49.04532741358583</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20.69249610378981</v>
+        <v>32.85635345946328</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5750065033399099</v>
+        <v>0.4852319860714957</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.128983302139772</v>
+        <v>-2.166266605633122</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6485</v>
+        <v>6292</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>418.9702530587876</v>
+        <v>424.5421983757583</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>72.3</v>
+        <v>53.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>29.76606734272728</v>
+        <v>38.53082018490008</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20.46498964484702</v>
+        <v>20.69249610378981</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.642517703886183</v>
+        <v>0.5750065033399099</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.7474719465605011</v>
+        <v>-1.128983302139772</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6237</v>
+        <v>6485</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>416.8083807252461</v>
+        <v>418.9702530587876</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>39</v>
+        <v>72.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>33.03350846355755</v>
+        <v>29.76606734272728</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.45772329174018</v>
+        <v>20.46498964484702</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.366474934973936</v>
+        <v>1.642517703886183</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.6407027004981471</v>
+        <v>-0.7474719465605011</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6209</v>
+        <v>6237</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>416.0812626751181</v>
+        <v>416.8083807252461</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>78.5</v>
+        <v>39</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45.93340868031385</v>
+        <v>33.03350846355755</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>24.51649089578654</v>
+        <v>17.45772329174018</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3702035097558356</v>
+        <v>1.366474934973936</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.929946674899901</v>
+        <v>-0.6407027004981471</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6419</v>
+        <v>6209</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>414.0122042960966</v>
+        <v>416.0812626751181</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>140</v>
+        <v>78.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45.98402673163703</v>
+        <v>45.93340868031385</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>9.449351149078778</v>
+        <v>24.51649089578654</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.8757486211390767</v>
+        <v>0.3702035097558356</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.4676167343005739</v>
+        <v>-0.929946674899901</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6235</v>
+        <v>6419</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>413.2177600491078</v>
+        <v>414.0122042960966</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>41.85</v>
+        <v>140</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.18897741254143</v>
+        <v>45.98402673163703</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>20.57008665580869</v>
+        <v>9.449351149078778</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6985693230643241</v>
+        <v>0.8757486211390767</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.2045763115179537</v>
+        <v>-0.4676167343005739</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6418</v>
+        <v>6235</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>406.8429724243285</v>
+        <v>413.2177600491078</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>31.6</v>
+        <v>41.85</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>47.09298874022041</v>
+        <v>49.18897741254143</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>21.02956918709781</v>
+        <v>20.57008665580869</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7713590932763663</v>
+        <v>0.6985693230643241</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0106988022320226</v>
+        <v>0.2045763115179537</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6225</v>
+        <v>6418</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>402.1577993409518</v>
+        <v>406.8429724243285</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>24.65</v>
+        <v>31.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>57.3362260238328</v>
+        <v>47.09298874022041</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>12.9042956026273</v>
+        <v>21.02956918709781</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8852516238374502</v>
+        <v>0.7713590932763663</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3650510747937034</v>
+        <v>0.0106988022320226</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6443</v>
+        <v>6225</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>401.5404220385802</v>
+        <v>402.1577993409518</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>29.9</v>
+        <v>24.65</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>26.64159535396048</v>
+        <v>57.3362260238328</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.46449600095472</v>
+        <v>12.9042956026273</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8401198999279204</v>
+        <v>0.8852516238374502</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.5220631061656777</v>
+        <v>0.3650510747937034</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6229</v>
+        <v>6443</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>399.4255812603826</v>
+        <v>401.5404220385802</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>25.15</v>
+        <v>29.9</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>37.52558879227758</v>
+        <v>26.64159535396048</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>11.81959021493813</v>
+        <v>21.46449600095472</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.842371892956683</v>
+        <v>0.8401198999279204</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.2182061318346616</v>
+        <v>-0.5220631061656777</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6274</v>
+        <v>6229</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>396.8338571981641</v>
+        <v>399.4255812603826</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1395</v>
+        <v>25.15</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>40.42357930003718</v>
+        <v>37.52558879227758</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21.69421044490271</v>
+        <v>11.81959021493813</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8969404449251456</v>
+        <v>0.842371892956683</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-39.03779958901974</v>
+        <v>-0.2182061318346616</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6415</v>
+        <v>6274</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>382.9739629109157</v>
+        <v>396.8338571981641</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>493.5</v>
+        <v>1395</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>39.51409580688221</v>
+        <v>40.42357930003718</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>17.22005754498739</v>
+        <v>21.69421044490271</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.349527226651387</v>
+        <v>0.8969404449251456</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-15.47700204623479</v>
+        <v>-39.03779958901974</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6205</v>
+        <v>6415</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>382.5387382881365</v>
+        <v>382.9739629109157</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>493.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>34.8736907587942</v>
+        <v>39.51409580688221</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14.18269045830293</v>
+        <v>17.22005754498739</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.452524503659709</v>
+        <v>1.349527226651387</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-1.022007468852595</v>
+        <v>-15.47700204623479</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3495,21 +3495,21 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6284</v>
+        <v>6205</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>381.6531111305977</v>
+        <v>382.5387382881365</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>88.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>37.19739015635709</v>
+        <v>34.8736907587942</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>27.65146485789521</v>
+        <v>14.18269045830293</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6766324159328948</v>
+        <v>1.452524503659709</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.43097334506536</v>
+        <v>-1.022007468852595</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6266</v>
+        <v>6284</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>381.2140594558505</v>
+        <v>381.6531111305977</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>25.75</v>
+        <v>88.3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>48.22095029730338</v>
+        <v>37.19739015635709</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>18.04470795880789</v>
+        <v>27.65146485789521</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.25197118076318</v>
+        <v>0.6766324159328948</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1347634912454213</v>
+        <v>-1.43097334506536</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6417</v>
+        <v>6266</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>376.7107922007785</v>
+        <v>381.2140594558505</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>126</v>
+        <v>25.75</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>40.01419347724675</v>
+        <v>48.22095029730338</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11.0412521752428</v>
+        <v>18.04470795880789</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.217331049868175</v>
+        <v>1.25197118076318</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.3556843416105742</v>
+        <v>0.1347634912454213</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6167</v>
+        <v>6417</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>372.7178834908256</v>
+        <v>376.7107922007785</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>11.45</v>
+        <v>126</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>41.27003858563258</v>
+        <v>40.01419347724675</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>11.70943752079538</v>
+        <v>11.0412521752428</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.178277935179947</v>
+        <v>2.217331049868175</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0582741354857481</v>
+        <v>-0.3556843416105742</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6451</v>
+        <v>6167</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>372.6783485636391</v>
+        <v>372.7178834908256</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>446.5</v>
+        <v>11.45</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>36.76387990670743</v>
+        <v>41.27003858563258</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.31708409573116</v>
+        <v>11.70943752079538</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7376273048708955</v>
+        <v>1.178277935179947</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-12.77505456404969</v>
+        <v>-0.0582741354857481</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6465</v>
+        <v>6451</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>372.5402631361913</v>
+        <v>372.6783485636391</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>58.5</v>
+        <v>446.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.59885171695983</v>
+        <v>36.76387990670743</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.9528561455305</v>
+        <v>20.31708409573116</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2669818770674678</v>
+        <v>0.7376273048708955</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.115284812949539</v>
+        <v>-12.77505456404969</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6227</v>
+        <v>6465</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>368.7685920376251</v>
+        <v>372.5402631361913</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>113.5</v>
+        <v>58.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>40.19144657966612</v>
+        <v>47.59885171695983</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>13.09724528162937</v>
+        <v>23.9528561455305</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.9193893591396248</v>
+        <v>0.2669818770674678</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.133655249159758</v>
+        <v>-1.115284812949539</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6442</v>
+        <v>6227</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>368.6053583101051</v>
+        <v>368.7685920376251</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>1315</v>
+        <v>113.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>29.60926502791627</v>
+        <v>40.19144657966612</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.99551080850005</v>
+        <v>13.09724528162937</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.312688864725637</v>
+        <v>0.9193893591396248</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-36.82129652012311</v>
+        <v>-1.133655249159758</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6210</v>
+        <v>6442</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>366.9147643073316</v>
+        <v>368.6053583101051</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>19.6</v>
+        <v>1315</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>41.1931391857586</v>
+        <v>29.60926502791627</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>25.00835979918803</v>
+        <v>19.99551080850005</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.304437976991969</v>
+        <v>1.312688864725637</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0562768731292877</v>
+        <v>-36.82129652012311</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6234</v>
+        <v>6210</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>366.2337961159953</v>
+        <v>366.9147643073316</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>41.8</v>
+        <v>19.6</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>42.63908648001475</v>
+        <v>41.1931391857586</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>13.30593343069177</v>
+        <v>25.00835979918803</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7117443964524764</v>
+        <v>1.304437976991969</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.4460458216929683</v>
+        <v>-0.0562768731292877</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6187</v>
+        <v>6234</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>366.2159185273893</v>
+        <v>366.2337961159953</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>985</v>
+        <v>41.8</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,49 +4050,49 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.06698879860128</v>
+        <v>42.63908648001475</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.26023453139005</v>
+        <v>13.30593343069177</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.025580039991501</v>
+        <v>0.7117443964524764</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-5.397623123770142</v>
+        <v>-0.4460458216929683</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6246</v>
+        <v>6187</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>363.7533576675421</v>
+        <v>366.2159185273893</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>15</v>
+        <v>985</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>42.77371202137275</v>
+        <v>44.06698879860128</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.1808926980715</v>
+        <v>10.26023453139005</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.223068346114142</v>
+        <v>1.025580039991501</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.08942814495892509</v>
+        <v>-5.397623123770142</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6290</v>
+        <v>6246</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>362.2746293900191</v>
+        <v>363.7533576675421</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>261</v>
+        <v>15</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>32.6730874893462</v>
+        <v>42.77371202137275</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12.50868202450303</v>
+        <v>19.1808926980715</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.063884358505862</v>
+        <v>0.223068346114142</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-4.921452550002244</v>
+        <v>-0.08942814495892509</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6164</v>
+        <v>6290</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>360.6053776049005</v>
+        <v>362.2746293900191</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13.7</v>
+        <v>261</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>48.49672087735072</v>
+        <v>32.6730874893462</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>23.45025372616109</v>
+        <v>12.50868202450303</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.9605377604900484</v>
+        <v>1.063884358505862</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0620116865662404</v>
+        <v>-4.921452550002244</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6206</v>
+        <v>6164</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>355.0214114414242</v>
+        <v>360.6053776049005</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>124.5</v>
+        <v>13.7</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>41.66044008894854</v>
+        <v>48.49672087735072</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.3993526592281</v>
+        <v>23.45025372616109</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.599874653617135</v>
+        <v>0.9605377604900484</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.4402883690968316</v>
+        <v>-0.0620116865662404</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6285</v>
+        <v>6206</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>353.7182814138533</v>
+        <v>355.0214114414242</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>247.5</v>
+        <v>124.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>43.99509232575771</v>
+        <v>41.66044008894854</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16.86016204026965</v>
+        <v>12.3993526592281</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.8262458371047874</v>
+        <v>1.599874653617135</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1459334389325057</v>
+        <v>-0.4402883690968316</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6192</v>
+        <v>6285</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>350.179914810241</v>
+        <v>353.7182814138533</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>118.5</v>
+        <v>247.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.83594752263559</v>
+        <v>43.99509232575771</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.38161482770333</v>
+        <v>16.86016204026965</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.155384127519485</v>
+        <v>0.8262458371047874</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0742815483490022</v>
+        <v>0.1459334389325057</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6198</v>
+        <v>6192</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>349.69404738657</v>
+        <v>350.179914810241</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>20.5</v>
+        <v>118.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.39640847124177</v>
+        <v>43.83594752263559</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7.692803218820803</v>
+        <v>19.38161482770333</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.130763359497941</v>
+        <v>1.155384127519485</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0059581152144742</v>
+        <v>0.0742815483490022</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6265</v>
+        <v>6198</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>348.1056451784334</v>
+        <v>349.69404738657</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>51.6</v>
+        <v>20.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46.98624824411662</v>
+        <v>50.39640847124177</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>17.24205651200507</v>
+        <v>7.692803218820803</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7763261876670863</v>
+        <v>1.130763359497941</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.3870059890735968</v>
+        <v>-0.0059581152144742</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6244</v>
+        <v>6265</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>346.9203932505982</v>
+        <v>348.1056451784334</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>26.3</v>
+        <v>51.6</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>42.68878932313834</v>
+        <v>46.98624824411662</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10.38887157695708</v>
+        <v>17.24205651200507</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7651161020593567</v>
+        <v>0.7763261876670863</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.07520170474858549</v>
+        <v>-0.3870059890735968</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6170</v>
+        <v>6244</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>345.950175458058</v>
+        <v>346.9203932505982</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>47</v>
+        <v>26.3</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>23.36379895595175</v>
+        <v>42.68878932313834</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>24.60389860858746</v>
+        <v>10.38887157695708</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.9950175458057948</v>
+        <v>0.7651161020593567</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.6729671986781935</v>
+        <v>-0.07520170474858549</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6183</v>
+        <v>6170</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>338.9495890611067</v>
+        <v>345.950175458058</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>90.3</v>
+        <v>47</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.06822188886712</v>
+        <v>23.36379895595175</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.38249643426477</v>
+        <v>24.60389860858746</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>3.179050052402776</v>
+        <v>0.9950175458057948</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.1362635912257156</v>
+        <v>-0.6729671986781935</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6278</v>
+        <v>6183</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>329.4485413213741</v>
+        <v>338.9495890611067</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>172.5</v>
+        <v>90.3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>36.38162916588394</v>
+        <v>51.06822188886712</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.54607410688623</v>
+        <v>14.38249643426477</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9830362111746036</v>
+        <v>3.179050052402776</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-3.481474913525322</v>
+        <v>0.1362635912257156</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6218</v>
+        <v>6278</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>328.3102954214162</v>
+        <v>329.4485413213741</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>35.35</v>
+        <v>172.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.36603184708997</v>
+        <v>36.38162916588394</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.28332129153037</v>
+        <v>16.54607410688623</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4209252815279932</v>
+        <v>0.9830362111746036</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0774408462700764</v>
+        <v>-3.481474913525322</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6263</v>
+        <v>6218</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>327.4741560737663</v>
+        <v>328.3102954214162</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>159</v>
+        <v>35.35</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>44.92644017530375</v>
+        <v>46.36603184708997</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.4345739636545</v>
+        <v>12.28332129153037</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5805602194820401</v>
+        <v>0.4209252815279932</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.2713411360657443</v>
+        <v>-0.0774408462700764</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6228</v>
+        <v>6263</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>320.4478280982292</v>
+        <v>327.4741560737663</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>18.75</v>
+        <v>159</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.67596291549098</v>
+        <v>44.92644017530375</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>4.739510299716707</v>
+        <v>11.4345739636545</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.1614863084772919</v>
+        <v>0.5805602194820401</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0666741145724401</v>
+        <v>-0.2713411360657443</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6269</v>
+        <v>6228</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>309.3837310458081</v>
+        <v>320.4478280982292</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>60</v>
+        <v>18.75</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>38.23952205606606</v>
+        <v>43.67596291549098</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.63417117170561</v>
+        <v>4.739510299716707</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4744321569779558</v>
+        <v>0.1614863084772919</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.620126038909394</v>
+        <v>-0.0666741145724401</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6474</v>
+        <v>6269</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>305.700055722182</v>
+        <v>309.3837310458081</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>37.75</v>
+        <v>60</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.49035333832146</v>
+        <v>38.23952205606606</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>12.59282850178999</v>
+        <v>16.63417117170561</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.732997299136763</v>
+        <v>0.4744321569779558</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.2090472196312595</v>
+        <v>-1.620126038909394</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6230</v>
+        <v>6474</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>296.4779290185654</v>
+        <v>305.700055722182</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>117</v>
+        <v>37.75</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>33.21820061077729</v>
+        <v>51.49035333832146</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>20.02141646277412</v>
+        <v>12.59282850178999</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.389592816647187</v>
+        <v>0.732997299136763</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.3518361059832724</v>
+        <v>0.2090472196312595</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6224</v>
+        <v>6230</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>291.5878095751237</v>
+        <v>296.4779290185654</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>65.09999999999999</v>
+        <v>117</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>38.56568738217332</v>
+        <v>33.21820061077729</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>16.34606692014184</v>
+        <v>20.02141646277412</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4951525534956524</v>
+        <v>1.389592816647187</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-1.654780150809652</v>
+        <v>-0.3518361059832724</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6426</v>
+        <v>6224</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>291.2912443665111</v>
+        <v>291.5878095751237</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>174.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>35.63045351623084</v>
+        <v>38.56568738217332</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.86358863166591</v>
+        <v>16.34606692014184</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.167674294080052</v>
+        <v>0.4951525534956524</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.7190824110689498</v>
+        <v>-1.654780150809652</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6222</v>
+        <v>6426</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>291.0507658850218</v>
+        <v>291.2912443665111</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>21.05</v>
+        <v>174.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>53.29301569694766</v>
+        <v>35.63045351623084</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.43099901688182</v>
+        <v>18.86358863166591</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.0337596615931521</v>
+        <v>1.167674294080052</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.043283788879231</v>
+        <v>-0.7190824110689498</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6449</v>
+        <v>6222</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>285.0995446872672</v>
+        <v>291.0507658850218</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>299</v>
+        <v>21.05</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.12054428140949</v>
+        <v>53.29301569694766</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>19.73477740124393</v>
+        <v>22.43099901688182</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8492615971883024</v>
+        <v>0.0337596615931521</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-9.893479674157629</v>
+        <v>0.043283788879231</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6189</v>
+        <v>6449</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>284.2276701317693</v>
+        <v>285.0995446872672</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>48.7</v>
+        <v>299</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>39.49296850962701</v>
+        <v>41.12054428140949</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.06425685688644</v>
+        <v>19.73477740124393</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.4295316801850264</v>
+        <v>0.8492615971883024</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.4722496839569764</v>
+        <v>-9.893479674157629</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6177</v>
+        <v>6189</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>276.1264197115435</v>
+        <v>284.2276701317693</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>46</v>
+        <v>48.7</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>51.61881626341807</v>
+        <v>39.49296850962701</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>18.99780273135849</v>
+        <v>17.06425685688644</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.8330854398701238</v>
+        <v>0.4295316801850264</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0528745458099427</v>
+        <v>-0.4722496839569764</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6201</v>
+        <v>6177</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>275.4892513544311</v>
+        <v>276.1264197115435</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>54.71732471813185</v>
+        <v>51.61881626341807</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>11.38686227734965</v>
+        <v>18.99780273135849</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.390292371835669</v>
+        <v>0.8330854398701238</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0834935661452299</v>
+        <v>-0.0528745458099427</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6275</v>
+        <v>6201</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>270.4764652265488</v>
+        <v>275.4892513544311</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>47.2</v>
+        <v>49</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.07935405816765</v>
+        <v>54.71732471813185</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>12.17477422049715</v>
+        <v>11.38686227734965</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4205446082861426</v>
+        <v>1.390292371835669</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.2187956952239476</v>
+        <v>0.0834935661452299</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6438</v>
+        <v>6275</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>260.6029795540129</v>
+        <v>270.4764652265488</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>146.5</v>
+        <v>47.2</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>40.54774104879657</v>
+        <v>42.07935405816765</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>18.62691308364133</v>
+        <v>12.17477422049715</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.9756356406444546</v>
+        <v>0.4205446082861426</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,48 +5499,48 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.5422033399528945</v>
+        <v>-0.2187956952239476</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6287</v>
+        <v>6438</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>元隆</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>259.8543676849137</v>
+        <v>260.6029795540129</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>146.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G96" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>68.1649009408622</v>
+        <v>40.54774104879657</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v/>
+        <v>18.62691308364133</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3819364013941486</v>
+        <v>0.9756356406444546</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,48 +5552,48 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0007658816175811</v>
+        <v>-0.5422033399528945</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6188</v>
+        <v>6287</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>元隆</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>259.6292011883092</v>
+        <v>259.8543676849137</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>74.7</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G97" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>37.62772541909963</v>
+        <v>68.1649009408622</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.91930159646145</v>
+        <v/>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.7696141874879655</v>
+        <v>0.3819364013941486</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0584074189094208</v>
+        <v>0.0007658816175811</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6412</v>
+        <v>6188</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>250.4131872897391</v>
+        <v>259.6292011883092</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>84.7</v>
+        <v>74.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>37.19025966352753</v>
+        <v>37.62772541909963</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.03357094318077</v>
+        <v>12.91930159646145</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.586414250988027</v>
+        <v>0.7696141874879655</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.982582111437918</v>
+        <v>0.0584074189094208</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6276</v>
+        <v>6412</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>245.6070938538272</v>
+        <v>250.4131872897391</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>22</v>
+        <v>84.7</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>37.49617181286206</v>
+        <v>37.19025966352753</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>26.82659258170631</v>
+        <v>15.03357094318077</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.7465550935977333</v>
+        <v>0.586414250988027</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.1385424044489842</v>
+        <v>-0.982582111437918</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6462</v>
+        <v>6276</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>244.7464946520089</v>
+        <v>245.6070938538272</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>35.02045405590901</v>
+        <v>37.49617181286206</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.87851063115524</v>
+        <v>26.82659258170631</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.9286696858680602</v>
+        <v>0.7465550935977333</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.195023686522253</v>
+        <v>0.1385424044489842</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6216</v>
+        <v>6462</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>238.3511881919617</v>
+        <v>244.7464946520089</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>22.45</v>
+        <v>103</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>43.20657680468909</v>
+        <v>35.02045405590901</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.41236000736643</v>
+        <v>15.87851063115524</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.030678064883663</v>
+        <v>0.9286696858680602</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.008828114240391901</v>
+        <v>-1.195023686522253</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6405</v>
+        <v>6216</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>237.4990815745029</v>
+        <v>238.3511881919617</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>50.7</v>
+        <v>22.45</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>34.61100809363336</v>
+        <v>43.20657680468909</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.31809573675181</v>
+        <v>12.41236000736643</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6461160343113512</v>
+        <v>1.030678064883663</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-1.41558113880728</v>
+        <v>-0.008828114240391901</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6233</v>
+        <v>6405</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>235.171344127022</v>
+        <v>237.4990815745029</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>23.5</v>
+        <v>50.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>39.75741040180026</v>
+        <v>34.61100809363336</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.62896885166013</v>
+        <v>17.31809573675181</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.052270377647765</v>
+        <v>0.6461160343113512</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1403493703086826</v>
+        <v>-1.41558113880728</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6470</v>
+        <v>6233</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>231.5005339878356</v>
+        <v>235.171344127022</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>47.9</v>
+        <v>23.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.72421759801351</v>
+        <v>39.75741040180026</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>11.09546478553805</v>
+        <v>12.62896885166013</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6152223718562313</v>
+        <v>1.052270377647765</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1980062985696654</v>
+        <v>-0.1403493703086826</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6185</v>
+        <v>6470</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>222.6177528118468</v>
+        <v>231.5005339878356</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14.1</v>
+        <v>47.9</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.58374481219309</v>
+        <v>41.72421759801351</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>19.14310177569389</v>
+        <v>11.09546478553805</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.242590111617816</v>
+        <v>0.6152223718562313</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0310075108387209</v>
+        <v>-0.1980062985696654</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6441</v>
+        <v>6185</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>221.7831602276097</v>
+        <v>222.6177528118468</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>21.55</v>
+        <v>14.1</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.48173383220052</v>
+        <v>45.58374481219309</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>11.74574450107455</v>
+        <v>19.14310177569389</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.8508076966278268</v>
+        <v>1.242590111617816</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0176799270372772</v>
+        <v>-0.0310075108387209</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6245</v>
+        <v>6441</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>210.9208609261408</v>
+        <v>221.7831602276097</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>21.55</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.11160645000965</v>
+        <v>41.48173383220052</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>11.30098175460776</v>
+        <v>11.74574450107455</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.433710039284467</v>
+        <v>0.8508076966278268</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0701709012049878</v>
+        <v>0.0176799270372772</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6456</v>
+        <v>6245</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>210.9022184448314</v>
+        <v>210.9208609261408</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>69.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>47.65328054623803</v>
+        <v>45.11160645000965</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>15.85000931423397</v>
+        <v>11.30098175460776</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.7928806080438562</v>
+        <v>1.433710039284467</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1290889810314852</v>
+        <v>0.0701709012049878</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6272</v>
+        <v>6456</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>205.7113644001642</v>
+        <v>210.9022184448314</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>28.35</v>
+        <v>69.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>30.75068179188202</v>
+        <v>47.65328054623803</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.70284379049217</v>
+        <v>15.85000931423397</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.507386985914051</v>
+        <v>0.7928806080438562</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.2199465819671382</v>
+        <v>0.1290889810314852</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6184</v>
+        <v>6272</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>201.5284695320717</v>
+        <v>205.7113644001642</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>42.75</v>
+        <v>28.35</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>21.7067753572328</v>
+        <v>30.75068179188202</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>34.44114025721152</v>
+        <v>18.70284379049217</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5640667553310904</v>
+        <v>1.507386985914051</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0986178352101091</v>
+        <v>-0.2199465819671382</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6283</v>
+        <v>6184</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>200.0298613719694</v>
+        <v>201.5284695320717</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>21.45</v>
+        <v>42.75</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>32.7694928214096</v>
+        <v>21.7067753572328</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>13.94562649781173</v>
+        <v>34.44114025721152</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.127619809163145</v>
+        <v>0.5640667553310904</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.2150769062753505</v>
+        <v>-0.0986178352101091</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6281</v>
+        <v>6283</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>194.2484742034145</v>
+        <v>200.0298613719694</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>51</v>
+        <v>21.45</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45.21343313459993</v>
+        <v>32.7694928214096</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>11.57926453141971</v>
+        <v>13.94562649781173</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.9455328105509712</v>
+        <v>1.127619809163145</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0208803092810386</v>
+        <v>-0.2150769062753505</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6194</v>
+        <v>6281</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>183.6932721629621</v>
+        <v>194.2484742034145</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>30.85</v>
+        <v>51</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>30.13177207455806</v>
+        <v>45.21343313459993</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.88462948715988</v>
+        <v>11.57926453141971</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.10423727540251</v>
+        <v>0.9455328105509712</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1225837440962292</v>
+        <v>-0.0208803092810386</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6236</v>
+        <v>6194</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>183.556595940344</v>
+        <v>183.6932721629621</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0</v>
+        <v>30.85</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>48.11588819305965</v>
+        <v>30.13177207455806</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7.200129296947315</v>
+        <v>15.88462948715988</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0</v>
+        <v>1.10423727540251</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.2813066918681137</v>
+        <v>-0.1225837440962292</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6203</v>
+        <v>6236</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>179.0561330299016</v>
+        <v>183.556595940344</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>39.73016105686408</v>
+        <v>48.11588819305965</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.11442929107164</v>
+        <v>7.200129296947315</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.594785460724666</v>
+        <v>0</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,62 +6559,115 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0498398485002162</v>
+        <v>-0.2813066918681137</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>海韻電</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>179.0561330299016</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>39.73016105686408</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>14.11442929107164</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>1.594785460724666</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.0498398485002162</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>6176</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>瑞儀</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>173.4786080870358</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>87.8</v>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>38.89484666945636</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>17.20806631027989</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>1.037845367598917</v>
       </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>0.4861338805234179</v>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
